--- a/downloads/forms/attendance-roster.xlsx
+++ b/downloads/forms/attendance-roster.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출석부" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'출석부'!$A$1:$T$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'출석부'!$A$1:$AE$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,29 +518,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.263157894736842" customWidth="1" min="1" max="1"/>
     <col width="10.52631578947368" customWidth="1" min="2" max="2"/>
     <col width="5.263157894736842" customWidth="1" min="3" max="3"/>
-    <col width="4.894736842105262" customWidth="1" min="4" max="4"/>
-    <col width="4.894736842105265" customWidth="1" min="5" max="5"/>
-    <col width="4.894736842105265" customWidth="1" min="6" max="6"/>
-    <col width="4.894736842105262" customWidth="1" min="7" max="7"/>
-    <col width="4.894736842105262" customWidth="1" min="8" max="8"/>
-    <col width="1.842105263157895" customWidth="1" min="9" max="9"/>
-    <col width="3.052631578947367" customWidth="1" min="10" max="10"/>
-    <col width="4.894736842105262" customWidth="1" min="11" max="11"/>
-    <col width="4.894736842105269" customWidth="1" min="12" max="12"/>
-    <col width="2.947368421052629" customWidth="1" min="13" max="13"/>
-    <col width="1.947368421052633" customWidth="1" min="14" max="14"/>
-    <col width="4.894736842105262" customWidth="1" min="15" max="15"/>
-    <col width="4.894736842105269" customWidth="1" min="16" max="16"/>
-    <col width="4.894736842105255" customWidth="1" min="17" max="17"/>
-    <col width="4.894736842105269" customWidth="1" min="18" max="18"/>
-    <col width="4.894736842105255" customWidth="1" min="19" max="19"/>
-    <col width="5.157894736842112" customWidth="1" min="20" max="20"/>
+    <col width="4.526315789473685" customWidth="1" min="4" max="4"/>
+    <col width="4.526315789473685" customWidth="1" min="5" max="5"/>
+    <col width="4.526315789473681" customWidth="1" min="6" max="6"/>
+    <col width="4.526315789473689" customWidth="1" min="7" max="7"/>
+    <col width="4.526315789473681" customWidth="1" min="8" max="8"/>
+    <col width="4.526315789473681" customWidth="1" min="9" max="9"/>
+    <col width="4.526315789473689" customWidth="1" min="10" max="10"/>
+    <col width="4.526315789473681" customWidth="1" min="11" max="11"/>
+    <col width="4.526315789473689" customWidth="1" min="12" max="12"/>
+    <col width="4.526315789473681" customWidth="1" min="13" max="13"/>
+    <col width="3.947368421052632" customWidth="1" min="14" max="14"/>
+    <col width="0.5789473684210497" customWidth="1" min="15" max="15"/>
+    <col width="4.526315789473681" customWidth="1" min="16" max="16"/>
+    <col width="4.526315789473697" customWidth="1" min="17" max="17"/>
+    <col width="4.526315789473681" customWidth="1" min="18" max="18"/>
+    <col width="1.631578947368418" customWidth="1" min="19" max="19"/>
+    <col width="2.894736842105263" customWidth="1" min="20" max="20"/>
+    <col width="4.526315789473681" customWidth="1" min="21" max="21"/>
+    <col width="4.526315789473681" customWidth="1" min="22" max="22"/>
+    <col width="4.526315789473697" customWidth="1" min="23" max="23"/>
+    <col width="4.526315789473681" customWidth="1" min="24" max="24"/>
+    <col width="4.526315789473681" customWidth="1" min="25" max="25"/>
+    <col width="4.526315789473681" customWidth="1" min="26" max="26"/>
+    <col width="4.526315789473681" customWidth="1" min="27" max="27"/>
+    <col width="4.526315789473697" customWidth="1" min="28" max="28"/>
+    <col width="4.526315789473681" customWidth="1" min="29" max="29"/>
+    <col width="4.526315789473681" customWidth="1" min="30" max="30"/>
+    <col width="6.315789473684211" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -550,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="25.51181102362205" customHeight="1">
+    <row r="2" ht="24.09448818897638" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>모 임 명</t>
@@ -563,29 +574,40 @@
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="5" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>기 간</t>
-        </is>
-      </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="n"/>
       <c r="L2" s="5" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      월      일  ~      월      일</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>기 간</t>
+        </is>
+      </c>
       <c r="P2" s="5" t="n"/>
       <c r="Q2" s="5" t="n"/>
       <c r="R2" s="5" t="n"/>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      월      일  ~      월      일</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="n"/>
+      <c r="W2" s="5" t="n"/>
+      <c r="X2" s="5" t="n"/>
+      <c r="Y2" s="5" t="n"/>
+      <c r="Z2" s="5" t="n"/>
+      <c r="AA2" s="5" t="n"/>
+      <c r="AB2" s="5" t="n"/>
+      <c r="AC2" s="5" t="n"/>
+      <c r="AD2" s="5" t="n"/>
+      <c r="AE2" s="3" t="n"/>
     </row>
     <row r="3" ht="8.503937007874017" customHeight="1"/>
-    <row r="4" ht="21.54330708661417" customHeight="1">
+    <row r="4" ht="19.2755905511811" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>번호</t>
@@ -603,23 +625,34 @@
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="7" t="n"/>
       <c r="R4" s="7" t="n"/>
       <c r="S4" s="7" t="n"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="7" t="n"/>
+      <c r="V4" s="7" t="n"/>
+      <c r="W4" s="7" t="n"/>
+      <c r="X4" s="7" t="n"/>
+      <c r="Y4" s="7" t="n"/>
+      <c r="Z4" s="7" t="n"/>
+      <c r="AA4" s="7" t="n"/>
+      <c r="AB4" s="7" t="n"/>
+      <c r="AC4" s="7" t="n"/>
+      <c r="AD4" s="7" t="n"/>
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>계</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="21.54330708661417" customHeight="1">
+    <row r="5" ht="19.2755905511811" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>1</t>
@@ -633,19 +666,30 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="3" t="n"/>
+      <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="21.54330708661417" customHeight="1">
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="4" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="19.2755905511811" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2</t>
@@ -659,19 +703,30 @@
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="21.54330708661417" customHeight="1">
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n"/>
+      <c r="AA6" s="4" t="n"/>
+      <c r="AB6" s="4" t="n"/>
+      <c r="AC6" s="4" t="n"/>
+      <c r="AD6" s="4" t="n"/>
+      <c r="AE6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="19.2755905511811" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>3</t>
@@ -685,19 +740,30 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="3" t="n"/>
+      <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="21.54330708661417" customHeight="1">
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="4" t="n"/>
+      <c r="V7" s="4" t="n"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="4" t="n"/>
+      <c r="AA7" s="4" t="n"/>
+      <c r="AB7" s="4" t="n"/>
+      <c r="AC7" s="4" t="n"/>
+      <c r="AD7" s="4" t="n"/>
+      <c r="AE7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="19.2755905511811" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>4</t>
@@ -711,19 +777,30 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="3" t="n"/>
+      <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="21.54330708661417" customHeight="1">
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="4" t="n"/>
+      <c r="X8" s="4" t="n"/>
+      <c r="Y8" s="4" t="n"/>
+      <c r="Z8" s="4" t="n"/>
+      <c r="AA8" s="4" t="n"/>
+      <c r="AB8" s="4" t="n"/>
+      <c r="AC8" s="4" t="n"/>
+      <c r="AD8" s="4" t="n"/>
+      <c r="AE8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="19.2755905511811" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>5</t>
@@ -737,19 +814,30 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="3" t="n"/>
+      <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="21.54330708661417" customHeight="1">
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="4" t="n"/>
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="4" t="n"/>
+      <c r="Y9" s="4" t="n"/>
+      <c r="Z9" s="4" t="n"/>
+      <c r="AA9" s="4" t="n"/>
+      <c r="AB9" s="4" t="n"/>
+      <c r="AC9" s="4" t="n"/>
+      <c r="AD9" s="4" t="n"/>
+      <c r="AE9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="19.2755905511811" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>6</t>
@@ -763,19 +851,30 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
-      <c r="J10" s="3" t="n"/>
+      <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="21.54330708661417" customHeight="1">
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="4" t="n"/>
+      <c r="V10" s="4" t="n"/>
+      <c r="W10" s="4" t="n"/>
+      <c r="X10" s="4" t="n"/>
+      <c r="Y10" s="4" t="n"/>
+      <c r="Z10" s="4" t="n"/>
+      <c r="AA10" s="4" t="n"/>
+      <c r="AB10" s="4" t="n"/>
+      <c r="AC10" s="4" t="n"/>
+      <c r="AD10" s="4" t="n"/>
+      <c r="AE10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="19.2755905511811" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>7</t>
@@ -789,19 +888,30 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="3" t="n"/>
+      <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="21.54330708661417" customHeight="1">
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="4" t="n"/>
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="4" t="n"/>
+      <c r="X11" s="4" t="n"/>
+      <c r="Y11" s="4" t="n"/>
+      <c r="Z11" s="4" t="n"/>
+      <c r="AA11" s="4" t="n"/>
+      <c r="AB11" s="4" t="n"/>
+      <c r="AC11" s="4" t="n"/>
+      <c r="AD11" s="4" t="n"/>
+      <c r="AE11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="19.2755905511811" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>8</t>
@@ -815,19 +925,30 @@
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
-      <c r="J12" s="3" t="n"/>
+      <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="3" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="21.54330708661417" customHeight="1">
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n"/>
+      <c r="W12" s="4" t="n"/>
+      <c r="X12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="4" t="n"/>
+      <c r="AA12" s="4" t="n"/>
+      <c r="AB12" s="4" t="n"/>
+      <c r="AC12" s="4" t="n"/>
+      <c r="AD12" s="4" t="n"/>
+      <c r="AE12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="19.2755905511811" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>9</t>
@@ -841,19 +962,30 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
-      <c r="J13" s="3" t="n"/>
+      <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
       <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="21.54330708661417" customHeight="1">
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="4" t="n"/>
+      <c r="V13" s="4" t="n"/>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="4" t="n"/>
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="4" t="n"/>
+      <c r="AA13" s="4" t="n"/>
+      <c r="AB13" s="4" t="n"/>
+      <c r="AC13" s="4" t="n"/>
+      <c r="AD13" s="4" t="n"/>
+      <c r="AE13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="19.2755905511811" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>10</t>
@@ -867,19 +999,30 @@
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="3" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="21.54330708661417" customHeight="1">
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n"/>
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="4" t="n"/>
+      <c r="Y14" s="4" t="n"/>
+      <c r="Z14" s="4" t="n"/>
+      <c r="AA14" s="4" t="n"/>
+      <c r="AB14" s="4" t="n"/>
+      <c r="AC14" s="4" t="n"/>
+      <c r="AD14" s="4" t="n"/>
+      <c r="AE14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="19.2755905511811" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>11</t>
@@ -893,19 +1036,30 @@
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="21.54330708661417" customHeight="1">
+      <c r="T15" s="3" t="n"/>
+      <c r="U15" s="4" t="n"/>
+      <c r="V15" s="4" t="n"/>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="4" t="n"/>
+      <c r="Z15" s="4" t="n"/>
+      <c r="AA15" s="4" t="n"/>
+      <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="4" t="n"/>
+      <c r="AD15" s="4" t="n"/>
+      <c r="AE15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="19.2755905511811" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t>12</t>
@@ -919,19 +1073,30 @@
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="3" t="n"/>
+      <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="3" t="n"/>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
-      <c r="T16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="21.54330708661417" customHeight="1">
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="4" t="n"/>
+      <c r="AA16" s="4" t="n"/>
+      <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="4" t="n"/>
+      <c r="AD16" s="4" t="n"/>
+      <c r="AE16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="19.2755905511811" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>13</t>
@@ -945,19 +1110,30 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="21.54330708661417" customHeight="1">
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="4" t="n"/>
+      <c r="V17" s="4" t="n"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n"/>
+      <c r="AA17" s="4" t="n"/>
+      <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="4" t="n"/>
+      <c r="AD17" s="4" t="n"/>
+      <c r="AE17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="19.2755905511811" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>14</t>
@@ -971,19 +1147,30 @@
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="3" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="21.54330708661417" customHeight="1">
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
+      <c r="W18" s="4" t="n"/>
+      <c r="X18" s="4" t="n"/>
+      <c r="Y18" s="4" t="n"/>
+      <c r="Z18" s="4" t="n"/>
+      <c r="AA18" s="4" t="n"/>
+      <c r="AB18" s="4" t="n"/>
+      <c r="AC18" s="4" t="n"/>
+      <c r="AD18" s="4" t="n"/>
+      <c r="AE18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="19.2755905511811" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>15</t>
@@ -997,19 +1184,30 @@
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="21.54330708661417" customHeight="1">
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="4" t="n"/>
+      <c r="V19" s="4" t="n"/>
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="4" t="n"/>
+      <c r="Y19" s="4" t="n"/>
+      <c r="Z19" s="4" t="n"/>
+      <c r="AA19" s="4" t="n"/>
+      <c r="AB19" s="4" t="n"/>
+      <c r="AC19" s="4" t="n"/>
+      <c r="AD19" s="4" t="n"/>
+      <c r="AE19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="19.2755905511811" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>16</t>
@@ -1023,19 +1221,30 @@
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="3" t="n"/>
+      <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="3" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="21.54330708661417" customHeight="1">
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="4" t="n"/>
+      <c r="Y20" s="4" t="n"/>
+      <c r="Z20" s="4" t="n"/>
+      <c r="AA20" s="4" t="n"/>
+      <c r="AB20" s="4" t="n"/>
+      <c r="AC20" s="4" t="n"/>
+      <c r="AD20" s="4" t="n"/>
+      <c r="AE20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="19.2755905511811" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>17</t>
@@ -1049,19 +1258,30 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
-      <c r="J21" s="3" t="n"/>
+      <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
       <c r="M21" s="4" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="3" t="n"/>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="21.54330708661417" customHeight="1">
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="4" t="n"/>
+      <c r="V21" s="4" t="n"/>
+      <c r="W21" s="4" t="n"/>
+      <c r="X21" s="4" t="n"/>
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="4" t="n"/>
+      <c r="AA21" s="4" t="n"/>
+      <c r="AB21" s="4" t="n"/>
+      <c r="AC21" s="4" t="n"/>
+      <c r="AD21" s="4" t="n"/>
+      <c r="AE21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="19.2755905511811" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>18</t>
@@ -1075,25 +1295,36 @@
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
-      <c r="J22" s="3" t="n"/>
+      <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="3" t="n"/>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="4" t="n"/>
       <c r="S22" s="4" t="n"/>
-      <c r="T22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="21.54330708661417" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="4" t="n"/>
+      <c r="Y22" s="4" t="n"/>
+      <c r="Z22" s="4" t="n"/>
+      <c r="AA22" s="4" t="n"/>
+      <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="4" t="n"/>
+      <c r="AD22" s="4" t="n"/>
+      <c r="AE22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="19.2755905511811" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>출석 인원</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
@@ -1101,357 +1332,107 @@
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
-      <c r="J23" s="3" t="n"/>
+      <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="3" t="n"/>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="n"/>
-      <c r="T23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="21.54330708661417" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n"/>
-      <c r="T24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="21.54330708661417" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="21.54330708661417" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="21.54330708661417" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n"/>
-      <c r="R27" s="4" t="n"/>
-      <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="21.54330708661417" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="21.54330708661417" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="4" t="n"/>
-      <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="4" t="n"/>
-      <c r="R29" s="4" t="n"/>
-      <c r="S29" s="4" t="n"/>
-      <c r="T29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="21.54330708661417" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="21.54330708661417" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
-      <c r="R31" s="4" t="n"/>
-      <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="21.54330708661417" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>출석 인원</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="4" t="n"/>
+      <c r="V23" s="4" t="n"/>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n"/>
+      <c r="Y23" s="4" t="n"/>
+      <c r="Z23" s="4" t="n"/>
+      <c r="AA23" s="4" t="n"/>
+      <c r="AB23" s="4" t="n"/>
+      <c r="AC23" s="4" t="n"/>
+      <c r="AD23" s="4" t="n"/>
+      <c r="AE23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>적는 법(예): ○ 출석 · △ 지각 · × 결석 — 맨 위 칸에 날짜를 적어요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="93">
+  <mergeCells count="66">
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="N16:O16"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="N22:O22"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="S8:T8"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="T2:AE2"/>
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="S23:T23"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N14:O14"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="A33:T33"/>
-    <mergeCell ref="N2:T2"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A24:AE24"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A1:AE1"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N9:O9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="O2:S2"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="N15:O15"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="N6:O6"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="N4:O4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5905511811023623" right="0.5905511811023623" top="0.5905511811023623" bottom="0.5905511811023623" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>